--- a/docs/16school/characterリスト.xlsx
+++ b/docs/16school/characterリスト.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6F54B4E108E3E434/ドキュメント/works/16job/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f54b4e108e3e434/ドキュメント/works/mobby/HP/docs/16school/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{A064C215-31D8-447E-AF39-14017729046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2907368A-1D4C-441A-99BC-54B8F6F04E0F}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{A064C215-31D8-447E-AF39-14017729046A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40E4BE10-59CB-40A7-9B50-753B9B2B4449}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{A4C20E54-849A-4E90-9BFE-642BF9C378F3}"/>
+    <workbookView xWindow="9975" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{A4C20E54-849A-4E90-9BFE-642BF9C378F3}"/>
   </bookViews>
   <sheets>
     <sheet name="仕事" sheetId="1" r:id="rId1"/>
     <sheet name="学校" sheetId="2" r:id="rId2"/>
+    <sheet name="ChatGPT" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="138">
   <si>
     <t>1. 左上：ロジカル・管理（整理整頓・効率化・安定）</t>
   </si>
@@ -656,6 +657,9 @@
   </si>
   <si>
     <t>style: minimalist 3D creature illustration, high quality render, no mouth,Right eye lens, clean, cute but professional, toy design --ar 1:1</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/6992d3f0-b92c-8013-b2d7-4693c6e95fa7</t>
   </si>
 </sst>
 </file>
@@ -1941,4 +1945,20 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257E78D7-3F4E-4A76-AA6B-6733BCB99E50}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17.649999999999999"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>